--- a/artfynd/A 2053-2023 artfynd.xlsx
+++ b/artfynd/A 2053-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129955585</v>
       </c>
       <c r="B2" t="n">
-        <v>58219</v>
+        <v>58222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129955583</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129955245</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2053-2023 artfynd.xlsx
+++ b/artfynd/A 2053-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129955585</v>
       </c>
       <c r="B2" t="n">
-        <v>58222</v>
+        <v>58223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129955583</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129955245</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2053-2023 artfynd.xlsx
+++ b/artfynd/A 2053-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129955585</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129955583</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129955245</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2053-2023 artfynd.xlsx
+++ b/artfynd/A 2053-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129955585</v>
+        <v>129955580</v>
       </c>
       <c r="B2" t="n">
-        <v>58309</v>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523464</v>
+        <v>523578</v>
       </c>
       <c r="R2" t="n">
-        <v>6334212</v>
+        <v>6334229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>03:23</t>
+          <t>03:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>03:23</t>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hörs österut på håll.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,27 +797,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129955583</v>
+        <v>129955582</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523489</v>
+        <v>523557</v>
       </c>
       <c r="R3" t="n">
-        <v>6334243</v>
+        <v>6334263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>03:24</t>
+          <t>03:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>03:24</t>
+          <t>03:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +917,7 @@
         <v>129955245</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,6 +1028,240 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129955583</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörtelek, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>523489</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6334243</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129955585</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mörtelek, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>523464</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6334212</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
